--- a/frontend/public/resources/template/项目导入模板.xlsx
+++ b/frontend/public/resources/template/项目导入模板.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,12 +418,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,11 +439,21 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>TL</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型不合法" error="类型必须为项目或产品" promptTitle="类型" prompt="请选择项目或产品" type="list">
+      <formula1>"项目,产品"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>